--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46221</v>
+        <v>46229</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46222</v>
+        <v>46228</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46222</v>
+        <v>46228</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46219</v>
+        <v>46227</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46222</v>
+        <v>46228</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46222</v>
+        <v>46228</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46221</v>
+        <v>46229</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46221</v>
+        <v>46229</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46222</v>
+        <v>46228</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46219</v>
+        <v>46229</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46220</v>
+        <v>46228</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46222</v>
+        <v>46228</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46226</v>
+        <v>46236</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46226</v>
+        <v>46233</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46228</v>
+        <v>46236</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46228</v>
+        <v>46236</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46228</v>
+        <v>46236</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46233</v>
+        <v>46243</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46234</v>
+        <v>46242</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46233</v>
+        <v>46242</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46242</v>
+        <v>46250</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46240</v>
+        <v>46249</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46242</v>
+        <v>46250</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46240</v>
+        <v>46250</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>
